--- a/Evaluasi Mandiri Optimisasi 2024_Nico Arie Angga Barus_G1D021065.xlsx
+++ b/Evaluasi Mandiri Optimisasi 2024_Nico Arie Angga Barus_G1D021065.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Optimisasi_Nico Arie Angga Barus_G1D021065\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E33A04F-64CD-4747-A4A9-D0B38C0DFD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5101D396-7E58-4E45-9765-58C0EB0E07F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -316,11 +316,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -329,13 +327,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -541,13 +541,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -594,7 +594,7 @@
       <c r="C7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="19" t="s">
         <v>40</v>
       </c>
     </row>
@@ -607,10 +607,10 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
@@ -643,7 +643,7 @@
       <c r="E12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="22" t="s">
         <v>42</v>
       </c>
     </row>
@@ -660,7 +660,7 @@
       <c r="E13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="22" t="s">
         <v>42</v>
       </c>
     </row>
@@ -677,7 +677,7 @@
       <c r="E14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="22" t="s">
         <v>42</v>
       </c>
     </row>
@@ -691,53 +691,53 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <v>4</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="14" t="s">
+      <c r="D16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>5</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="14" t="s">
+      <c r="D17" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>6</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="14" t="s">
+      <c r="D18" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="23" t="s">
         <v>45</v>
       </c>
     </row>
@@ -754,16 +754,16 @@
       <c r="B20" s="6">
         <v>7</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="17" t="s">
+      <c r="D20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="22" t="s">
         <v>46</v>
       </c>
     </row>
@@ -771,16 +771,16 @@
       <c r="B21" s="6">
         <v>8</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="17" t="s">
+      <c r="D21" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="22" t="s">
         <v>47</v>
       </c>
     </row>
@@ -794,53 +794,53 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>9</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="14" t="s">
+      <c r="D23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="23" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>10</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="14" t="s">
+      <c r="D24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="23" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>11</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="14" t="s">
+      <c r="D25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>50</v>
       </c>
     </row>
@@ -854,26 +854,26 @@
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="18">
+      <c r="B27" s="16">
         <v>12</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="17"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="18">
+      <c r="B28" s="16">
         <v>13</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="17"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
@@ -885,45 +885,45 @@
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>14</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="14" t="s">
+      <c r="D30" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="19">
+      <c r="B31" s="17">
         <v>15</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
     </row>
     <row r="33" spans="3:3" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="3:3" ht="82" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="18" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="35" spans="3:3" ht="79.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="18" t="s">
         <v>36</v>
       </c>
     </row>
@@ -944,9 +944,21 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F12" r:id="rId2" xr:uid="{397AF579-03B3-43F2-A1FD-68C1E596E923}"/>
+    <hyperlink ref="F13" r:id="rId3" xr:uid="{9BD66E31-C5AA-4038-919C-661CD4423CF0}"/>
+    <hyperlink ref="F14" r:id="rId4" xr:uid="{AB2BA3B4-9507-4843-9D33-9E8337D118C9}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{FE3A3ADF-1E33-44FA-894C-E7CD9023DBBD}"/>
+    <hyperlink ref="F17" r:id="rId6" xr:uid="{FE61CDD6-AC6A-4DFC-85C9-E70C41E9270C}"/>
+    <hyperlink ref="F18" r:id="rId7" xr:uid="{87E94E0A-489B-43B6-B0B1-8D7A7665B749}"/>
+    <hyperlink ref="F20" r:id="rId8" xr:uid="{E6886F25-E112-4FCF-9A49-54F763E49552}"/>
+    <hyperlink ref="F21" r:id="rId9" xr:uid="{73E62487-26A5-4EEF-8E10-2ADA2BAB3133}"/>
+    <hyperlink ref="F23" r:id="rId10" xr:uid="{FF701845-FC17-44DB-B73B-698B22CAE9B8}"/>
+    <hyperlink ref="F24" r:id="rId11" xr:uid="{571E6798-7218-49E3-96DA-3652FAD3ED0E}"/>
+    <hyperlink ref="F25" r:id="rId12" xr:uid="{DD487986-7509-443A-A549-8C8172AB0186}"/>
+    <hyperlink ref="F30" r:id="rId13" xr:uid="{6B13C35A-5EF3-4959-8DB5-7ADCE317D4FF}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
